--- a/Account/students导入模板.xlsx
+++ b/Account/students导入模板.xlsx
@@ -68,13 +68,13 @@
     <t>Dr. Alice Johnson</t>
   </si>
   <si>
-    <t>上</t>
+    <t>下</t>
   </si>
   <si>
     <t>2101</t>
   </si>
   <si>
-    <t>2024-09-01</t>
+    <t>2025-03-03</t>
   </si>
   <si>
     <t>08:30:00</t>
@@ -89,7 +89,7 @@
     <t>2102</t>
   </si>
   <si>
-    <t>2024-09-02</t>
+    <t>2025-03-04</t>
   </si>
   <si>
     <t>15:40:00</t>
@@ -1321,7 +1321,7 @@
         <v>12</v>
       </c>
       <c r="D2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -1356,7 +1356,7 @@
         <v>12</v>
       </c>
       <c r="D3">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -1391,7 +1391,7 @@
         <v>12</v>
       </c>
       <c r="D4">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -1426,7 +1426,7 @@
         <v>12</v>
       </c>
       <c r="D5">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -1461,7 +1461,7 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -1496,7 +1496,7 @@
         <v>12</v>
       </c>
       <c r="D7">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E7">
         <v>2</v>
